--- a/WorkBot/main/data/order_archive/US Foods/US Foods_Triphammer_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/US Foods/US Foods_Triphammer_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1004,363 +1004,6 @@
         <v>20.59</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>3791747</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Can - Roasted Red Pepper (Strips)</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="n">
-        <v>50.32</v>
-      </c>
-      <c r="E31" t="n">
-        <v>50.32</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>7058803</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Can - Tomato - Whole Peeled</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" t="n">
-        <v>39.31</v>
-      </c>
-      <c r="E32" t="n">
-        <v>78.62</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>8457368</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Oil - Corn</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" t="n">
-        <v>43.36</v>
-      </c>
-      <c r="E33" t="n">
-        <v>86.72</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1365278</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Vegan Chicken Tenders</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>86.34</v>
-      </c>
-      <c r="E34" t="n">
-        <v>86.34</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>4254710</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Veggie Burger</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="n">
-        <v>51.47</v>
-      </c>
-      <c r="E35" t="n">
-        <v>51.47</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>7520950</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Can - Pizza Sauce</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" t="n">
-        <v>42.05</v>
-      </c>
-      <c r="E36" t="n">
-        <v>84.09999999999999</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1027629</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Cheddar - (Sliced)</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>12</v>
-      </c>
-      <c r="D37" t="n">
-        <v>42.38</v>
-      </c>
-      <c r="E37" t="n">
-        <v>508.56</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>9970237</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Chicken Filet - Breaded 4 oz (Raw)</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>10</v>
-      </c>
-      <c r="D38" t="n">
-        <v>27.47</v>
-      </c>
-      <c r="E38" t="n">
-        <v>274.7</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>3018439</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Cracker - Asst Bulk</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>60.82</v>
-      </c>
-      <c r="E39" t="n">
-        <v>60.82</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>1035842</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Feta - Pail</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>95.89</v>
-      </c>
-      <c r="E40" t="n">
-        <v>95.89</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>6432884</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Pepper Jack (Sliced)</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="E41" t="n">
-        <v>158.8</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>1028165</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Pickle - Dill Chip</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" t="n">
-        <v>32.74</v>
-      </c>
-      <c r="E42" t="n">
-        <v>65.48</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>1028188</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Tortellini - Cheese</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="n">
-        <v>27.26</v>
-      </c>
-      <c r="E43" t="n">
-        <v>27.26</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>4157160</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Spanakopita</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="n">
-        <v>72.31999999999999</v>
-      </c>
-      <c r="E44" t="n">
-        <v>72.31999999999999</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2742112</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Relish - Sweet</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
-        <v>34.58</v>
-      </c>
-      <c r="E45" t="n">
-        <v>34.58</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>4052171</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Apple Red - Fresh</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="E46" t="n">
-        <v>27.25</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>9546982</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Arugula - Fresh</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>4</v>
-      </c>
-      <c r="D47" t="n">
-        <v>20.16</v>
-      </c>
-      <c r="E47" t="n">
-        <v>80.64</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
